--- a/03_Bug_Reporting/Bug_Reports.xlsx
+++ b/03_Bug_Reporting/Bug_Reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\BookStack Demo WebTesting\BookStackDemo_WebTesting\03_Bug_Reporting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C84BD3-E5F5-4F78-A1F1-EA090F04E2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5053EE54-C667-4DEA-A4F9-B16D08AD551D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
   <si>
     <t>Key</t>
   </si>
@@ -150,9 +150,6 @@
     <t>System should restrict input and display duplication error.</t>
   </si>
   <si>
-    <t>System accepts input.</t>
-  </si>
-  <si>
     <t>Evidence\BUG_001.jpg</t>
   </si>
   <si>
@@ -181,6 +178,12 @@
   </si>
   <si>
     <t>New</t>
+  </si>
+  <si>
+    <t>System accepts input in Books name.</t>
+  </si>
+  <si>
+    <t>System accepts input in Shelf name.</t>
   </si>
 </sst>
 </file>
@@ -886,7 +889,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>31</v>
@@ -916,13 +919,13 @@
         <v>39</v>
       </c>
       <c r="L14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -930,13 +933,13 @@
         <v>30</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>34</v>
@@ -948,25 +951,25 @@
         <v>35</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>39</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
